--- a/data/s2/Annelinn/archetypes/stats_trans.xlsx
+++ b/data/s2/Annelinn/archetypes/stats_trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s2\Annelinn\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA85755D-3916-45D2-9F2C-9405056543C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09810EB-2972-4518-982A-C15D2A69486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D3">
         <v>0.03</v>
@@ -522,7 +522,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D5">
         <v>0.03</v>
@@ -562,7 +562,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
         <v>0.03</v>
@@ -602,7 +602,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
         <v>0.03</v>
@@ -642,7 +642,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
         <v>0.04</v>
@@ -682,7 +682,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
         <v>0.03</v>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="C15">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D15">
         <v>0.04</v>
@@ -762,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D17">
         <v>0.05</v>
